--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_71_R8.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_71_R8.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S. SHIELDS</t>
+          <t>N. SESTINA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2244</v>
+        <v>3.8857</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7515</v>
+        <v>2.4577</v>
       </c>
       <c r="F2" t="n">
-        <v>2.473</v>
+        <v>1.4279</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7867</v>
+        <v>1.3086</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9436</v>
+        <v>1.593</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8431</v>
+        <v>-0.2844</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6932</v>
+        <v>1.523</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8942</v>
+        <v>1.6469</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.201</v>
+        <v>-0.1239</v>
       </c>
       <c r="M2" t="n">
-        <v>1.0936</v>
+        <v>-0.2144</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0495</v>
+        <v>-0.0539</v>
       </c>
       <c r="O2" t="n">
-        <v>1.0441</v>
+        <v>-0.1605</v>
       </c>
       <c r="P2" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5975</v>
+        <v>-0.2812</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6097</v>
+        <v>-0.1375</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0123</v>
+        <v>-0.1436</v>
       </c>
       <c r="V2" t="n">
-        <v>1.6083</v>
+        <v>1.4665</v>
       </c>
       <c r="W2" t="n">
-        <v>1.6083</v>
+        <v>1.0722</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. SESTINA</t>
+          <t>S. SHIELDS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4332</v>
+        <v>3.5345</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0725</v>
+        <v>1.3976</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3607</v>
+        <v>2.1369</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3086</v>
+        <v>1.7867</v>
       </c>
       <c r="H3" t="n">
-        <v>1.593</v>
+        <v>0.9436</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2844</v>
+        <v>0.8431</v>
       </c>
       <c r="J3" t="n">
-        <v>1.523</v>
+        <v>0.6932</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6469</v>
+        <v>0.8942</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.1239</v>
+        <v>-0.201</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2144</v>
+        <v>1.0936</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0539</v>
+        <v>0.0495</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1605</v>
+        <v>1.0441</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R3" t="n">
         <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7336</v>
+        <v>-0.0925</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5228</v>
+        <v>0.2559</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2109</v>
+        <v>-0.3484</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4665</v>
+        <v>1.6083</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0722</v>
+        <v>1.6083</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. DUNSTON</t>
+          <t>Q. ELLIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.696</v>
+        <v>3.2885</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5039</v>
+        <v>1.1846</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1922</v>
+        <v>2.1039</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.0273</v>
+        <v>0.8191000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6627</v>
+        <v>-1.222</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3647</v>
+        <v>2.0411</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.1059</v>
+        <v>-0.0206</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.43</v>
+        <v>-0.9137999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6758999999999999</v>
+        <v>0.8932</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0785</v>
+        <v>0.8397</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2327</v>
+        <v>-0.3082</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3113</v>
+        <v>1.1479</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7956</v>
+        <v>0.2348</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5375</v>
+        <v>0.2205</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.742</v>
+        <v>0.0143</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0722</v>
+        <v>2.0026</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0722</v>
+        <v>2.1444</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Q. ELLIS</t>
+          <t>D. BOOKER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4321</v>
+        <v>3.2473</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5634</v>
+        <v>2.7294</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8686</v>
+        <v>0.5178</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8191000000000001</v>
+        <v>2.159</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.222</v>
+        <v>1.222</v>
       </c>
       <c r="I5" t="n">
-        <v>2.0411</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0206</v>
+        <v>1.1405</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.9137999999999999</v>
+        <v>1.3514</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8932</v>
+        <v>-0.2109</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8397</v>
+        <v>1.0185</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3082</v>
+        <v>-0.1294</v>
       </c>
       <c r="O5" t="n">
         <v>1.1479</v>
       </c>
       <c r="P5" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6216</v>
+        <v>-0.3756</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4007</v>
+        <v>-0.0193</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.221</v>
+        <v>-0.3563</v>
       </c>
       <c r="V5" t="n">
-        <v>2.0026</v>
+        <v>0.5361</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1444</v>
+        <v>1.6083</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. BOOKER</t>
+          <t>B. DUNSTON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2962</v>
+        <v>1.9683</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7111</v>
+        <v>0.4737</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5851</v>
+        <v>1.4946</v>
       </c>
       <c r="G6" t="n">
-        <v>2.159</v>
+        <v>-1.0273</v>
       </c>
       <c r="H6" t="n">
-        <v>1.222</v>
+        <v>-0.6627</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9370000000000001</v>
+        <v>-0.3647</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1405</v>
+        <v>-1.1059</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3514</v>
+        <v>-0.43</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.2109</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>1.0185</v>
+        <v>0.0785</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1294</v>
+        <v>-0.2327</v>
       </c>
       <c r="O6" t="n">
-        <v>1.1479</v>
+        <v>0.3113</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3267</v>
+        <v>0.0679</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0376</v>
+        <v>0.5074</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.289</v>
+        <v>-0.4395</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="W6" t="n">
-        <v>1.6083</v>
+        <v>1.0722</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1517</v>
+        <v>1.3085</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2517</v>
+        <v>1.4758</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1</v>
+        <v>-0.1672</v>
       </c>
       <c r="G7" t="n">
         <v>1.4468</v>
@@ -1000,13 +1000,13 @@
         <v>1.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1353</v>
+        <v>0.0215</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1845</v>
+        <v>0.0395</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0492</v>
+        <v>-0.018</v>
       </c>
       <c r="V7" t="n">
         <v>0.5361</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. RICCI</t>
+          <t>N. MANNION</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0773</v>
+        <v>0.4336</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2361</v>
+        <v>-0.4988</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8411999999999999</v>
+        <v>0.9324</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7598</v>
+        <v>1.044</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3349</v>
+        <v>-0.7997</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.425</v>
+        <v>1.8436</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.4957</v>
+        <v>0.7866</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7121</v>
+        <v>-0.7458</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.7836</v>
+        <v>1.5324</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7359</v>
+        <v>0.2574</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6227</v>
+        <v>-0.0539</v>
       </c>
       <c r="O8" t="n">
-        <v>1.3586</v>
+        <v>0.3113</v>
       </c>
       <c r="P8" t="n">
         <v>0.232</v>
@@ -1078,22 +1078,22 @@
         <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>2.7469</v>
+        <v>-0.8424</v>
       </c>
       <c r="T8" t="n">
-        <v>2.8194</v>
+        <v>-0.1256</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0725</v>
+        <v>-0.7167</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. MANNION</t>
+          <t>G. RICCI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,40 +1189,40 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0551</v>
+        <v>-0.8018</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0453</v>
+        <v>-1.3405</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1004</v>
+        <v>0.5387</v>
       </c>
       <c r="G10" t="n">
-        <v>1.044</v>
+        <v>-1.7598</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7997</v>
+        <v>-1.3349</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8436</v>
+        <v>-0.425</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7866</v>
+        <v>-2.4957</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7458</v>
+        <v>-0.7121</v>
       </c>
       <c r="L10" t="n">
-        <v>1.5324</v>
+        <v>-1.7836</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2574</v>
+        <v>0.7359</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0539</v>
+        <v>-0.6227</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3113</v>
+        <v>1.3586</v>
       </c>
       <c r="P10" t="n">
         <v>0.232</v>
@@ -1234,22 +1234,22 @@
         <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2208</v>
+        <v>0.8678</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6721</v>
+        <v>1.2428</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5487</v>
+        <v>-0.3749</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4841</v>
+        <v>-1.243</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4551</v>
+        <v>-1.1131</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0291</v>
+        <v>-0.1299</v>
       </c>
       <c r="G11" t="n">
         <v>1.2251</v>
@@ -1312,13 +1312,13 @@
         <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.315</v>
+        <v>-0.0738</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1845</v>
+        <v>0.1575</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1305</v>
+        <v>-0.2313</v>
       </c>
       <c r="V11" t="n">
         <v>-1.4665</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8377</v>
+        <v>-1.4572</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4469</v>
+        <v>-2.5033</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6092</v>
+        <v>1.0461</v>
       </c>
       <c r="G12" t="n">
         <v>-0.6522</v>
@@ -1390,13 +1390,13 @@
         <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.9536</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.963</v>
+        <v>-0.0193</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9906</v>
+        <v>-0.5537</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,31 +1423,31 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>13.4123</v>
+        <v>14.5325</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1218</v>
+        <v>4.241999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>10.2905</v>
+        <v>10.2904</v>
       </c>
       <c r="G13" t="n">
         <v>6.7181</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.467000000000001</v>
+        <v>-2.467</v>
       </c>
       <c r="I13" t="n">
         <v>9.184800000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>1.2328</v>
+        <v>1.232800000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6561999999999997</v>
+        <v>-0.6561999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>1.8892</v>
+        <v>1.889200000000001</v>
       </c>
       <c r="M13" t="n">
         <v>5.4852</v>
@@ -1456,7 +1456,7 @@
         <v>-1.8105</v>
       </c>
       <c r="O13" t="n">
-        <v>7.295800000000001</v>
+        <v>7.295799999999999</v>
       </c>
       <c r="P13" t="n">
         <v>3.4794</v>
@@ -1468,16 +1468,16 @@
         <v>13.9171</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.398600000000001</v>
+        <v>-1.2786</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9267</v>
+        <v>2.0472</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.3256</v>
+        <v>-3.3254</v>
       </c>
       <c r="V13" t="n">
-        <v>5.613499999999999</v>
+        <v>5.6135</v>
       </c>
       <c r="W13" t="n">
         <v>11.3999</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L. CAVALIERE</t>
+          <t>I. BAKO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2166</v>
+        <v>1.1483</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.8091</v>
+        <v>0.8931</v>
       </c>
       <c r="F14" t="n">
-        <v>3.0257</v>
+        <v>0.2552</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9336</v>
+        <v>0.5986</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2042</v>
+        <v>0.6855</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7294</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0598</v>
+        <v>0.645</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1008</v>
+        <v>0.5714</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1607</v>
+        <v>0.0736</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9935</v>
+        <v>-0.0464</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1034</v>
+        <v>0.1141</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8901</v>
+        <v>-0.1605</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2829</v>
+        <v>0.1759</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5895</v>
+        <v>0.1063</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.0696</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. BAKO</t>
+          <t>L. CAVALIERE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5756</v>
+        <v>1.1164</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4213</v>
+        <v>-1.5732</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1544</v>
+        <v>2.6896</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5986</v>
+        <v>0.9336</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6855</v>
+        <v>0.2042</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.08690000000000001</v>
+        <v>0.7294</v>
       </c>
       <c r="J15" t="n">
-        <v>0.645</v>
+        <v>-0.0598</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5714</v>
+        <v>0.1008</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0736</v>
+        <v>-0.1607</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0464</v>
+        <v>0.9935</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1141</v>
+        <v>0.1034</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1605</v>
+        <v>0.8901</v>
       </c>
       <c r="P15" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3967</v>
+        <v>0.1828</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3655</v>
+        <v>-0.3536</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0312</v>
+        <v>0.5364</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. ROBINSON</t>
+          <t>D. HOMMES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0772</v>
+        <v>0.5039</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3996</v>
+        <v>0.0541</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.4767</v>
+        <v>0.4498</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.0021</v>
+        <v>-0.3896</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.383</v>
+        <v>-0.0216</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.619</v>
+        <v>-0.368</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4132</v>
+        <v>0.0539</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.4433</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8564000000000001</v>
+        <v>-0.7863</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4152</v>
+        <v>-0.4435</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0602</v>
+        <v>-0.8618</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.4755</v>
+        <v>0.4183</v>
       </c>
       <c r="P16" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0873</v>
+        <v>0.1977</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3961</v>
+        <v>0.0002</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3088</v>
+        <v>0.1975</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.7501</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. DOKOSSI</t>
+          <t>S. HERRERA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.152</v>
+        <v>0.3138</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4829</v>
+        <v>1.4282</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6349</v>
+        <v>-1.1144</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4979</v>
+        <v>1.2606</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0733</v>
+        <v>0.9462</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5754</v>
+        <v>0.3144</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7658</v>
+        <v>1.9322</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6554</v>
+        <v>0.4033</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1104</v>
+        <v>1.5289</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2679</v>
+        <v>-0.6716</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4179</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6859</v>
+        <v>-1.2144</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3348</v>
+        <v>-1.037</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2829</v>
+        <v>-0.4165</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6177</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.1444</v>
+        <v>-0.1418</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.1444</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. HOMMES</t>
+          <t>A. DOKOSSI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2539</v>
+        <v>-0.1507</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5356</v>
+        <v>0.9547</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2818</v>
+        <v>-1.1054</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3896</v>
+        <v>0.4979</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0216</v>
+        <v>1.0733</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.368</v>
+        <v>-0.5754</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0539</v>
+        <v>0.7658</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8401999999999999</v>
+        <v>0.6554</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7863</v>
+        <v>0.1104</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4435</v>
+        <v>-0.2679</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8618</v>
+        <v>0.4179</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4183</v>
+        <v>-0.6859</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5601</v>
+        <v>0.3361</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5895</v>
+        <v>0.1889</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0294</v>
+        <v>0.1472</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. HERRERA</t>
+          <t>J. ROBINSON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3489</v>
+        <v>-0.8527</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9563</v>
+        <v>1.456</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3053</v>
+        <v>-2.3087</v>
       </c>
       <c r="G19" t="n">
-        <v>1.2606</v>
+        <v>-1.0021</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9462</v>
+        <v>-0.383</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3144</v>
+        <v>-0.619</v>
       </c>
       <c r="J19" t="n">
-        <v>1.9322</v>
+        <v>0.4132</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4033</v>
+        <v>-0.4433</v>
       </c>
       <c r="L19" t="n">
-        <v>1.5289</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6716</v>
+        <v>-1.4152</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.0602</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2144</v>
+        <v>-1.4755</v>
       </c>
       <c r="P19" t="n">
         <v>0.232</v>
@@ -1936,28 +1936,28 @@
         <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.6996</v>
+        <v>0.3117</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8883</v>
+        <v>0.4525</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8114</v>
+        <v>-0.1408</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1418</v>
+        <v>-0.3943</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0722</v>
+        <v>1.7501</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.214</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. FAYE</t>
+          <t>J. AYAYI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5601</v>
+        <v>-1.2747</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6004</v>
+        <v>0.0813</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1606</v>
+        <v>-1.356</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.003</v>
+        <v>-0.3619</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3878</v>
+        <v>0.6519</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3849</v>
+        <v>-1.0138</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.9242</v>
+        <v>-0.662</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9978</v>
+        <v>0.8739</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0736</v>
+        <v>-1.5359</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.07870000000000001</v>
+        <v>0.3001</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.39</v>
+        <v>-0.222</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3113</v>
+        <v>0.5221</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3706</v>
+        <v>1.2316</v>
       </c>
       <c r="T20" t="n">
-        <v>1.6122</v>
+        <v>0.7433</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2416</v>
+        <v>0.4883</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.181</v>
+        <v>-1.2761</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8386</v>
+        <v>-1.9566</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6577</v>
+        <v>0.6805</v>
       </c>
       <c r="G21" t="n">
         <v>-1.1636</v>
@@ -2092,13 +2092,13 @@
         <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3743</v>
+        <v>0.2792</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3936</v>
+        <v>0.2756</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0193</v>
+        <v>0.0035</v>
       </c>
       <c r="V21" t="n">
         <v>0.5361</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. AYAYI</t>
+          <t>M. FAYE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7802</v>
+        <v>-1.5317</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3905</v>
+        <v>-0.4611</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3896</v>
+        <v>-1.0705</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3619</v>
+        <v>-1.003</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6519</v>
+        <v>-1.3878</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0138</v>
+        <v>0.3849</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.662</v>
+        <v>-0.9242</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8739</v>
+        <v>-0.9978</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.5359</v>
+        <v>0.0736</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3001</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.222</v>
+        <v>-0.39</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5221</v>
+        <v>0.3113</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7262</v>
+        <v>0.3991</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2715</v>
+        <v>0.5507</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4547</v>
+        <v>-0.1516</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5401</v>
+        <v>-2.4</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2484</v>
+        <v>-3.3664</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7083</v>
+        <v>0.9664</v>
       </c>
       <c r="G23" t="n">
         <v>-1.7725</v>
@@ -2248,13 +2248,13 @@
         <v>0.6959</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2324</v>
+        <v>0.3725</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8417</v>
+        <v>0.7237</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6093</v>
+        <v>-0.3512</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5361</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.7506</v>
+        <v>-2.7182</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.6096</v>
+        <v>-3.1378</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.141</v>
+        <v>0.4195</v>
       </c>
       <c r="G24" t="n">
         <v>-2.4223</v>
@@ -2326,13 +2326,13 @@
         <v>1.3917</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1659</v>
+        <v>-0.1336</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.094</v>
+        <v>0.3778</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0719</v>
+        <v>-0.5113</v>
       </c>
       <c r="V24" t="n">
         <v>-0.3943</v>
@@ -2359,10 +2359,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.5605</v>
+        <v>-5.5041</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.6468</v>
+        <v>-3.5904</v>
       </c>
       <c r="F25" t="n">
         <v>-1.9137</v>
@@ -2404,10 +2404,10 @@
         <v>0.6959</v>
       </c>
       <c r="S25" t="n">
-        <v>1.8125</v>
+        <v>0.8689</v>
       </c>
       <c r="T25" t="n">
-        <v>1.6201</v>
+        <v>0.6765</v>
       </c>
       <c r="U25" t="n">
         <v>0.1924</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-13.4123</v>
+        <v>-12.6258</v>
       </c>
       <c r="E26" t="n">
         <v>-9.2181</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.1939</v>
+        <v>-3.4077</v>
       </c>
       <c r="G26" t="n">
-        <v>-6.718099999999999</v>
+        <v>-6.7181</v>
       </c>
       <c r="H26" t="n">
-        <v>2.4669</v>
+        <v>2.466900000000001</v>
       </c>
       <c r="I26" t="n">
         <v>-9.184799999999999</v>
@@ -2482,13 +2482,13 @@
         <v>10.4381</v>
       </c>
       <c r="S26" t="n">
-        <v>2.3987</v>
+        <v>3.1849</v>
       </c>
       <c r="T26" t="n">
-        <v>3.3255</v>
+        <v>3.3254</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.9267999999999997</v>
+        <v>-0.1405000000000002</v>
       </c>
       <c r="V26" t="n">
         <v>-5.613500000000001</v>
